--- a/skills/family-finance/assets/family-finance-template.xlsx
+++ b/skills/family-finance/assets/family-finance-template.xlsx
@@ -331,6 +331,27 @@
           <t>1月</t>
         </is>
       </c>
+      <c r="Q3">
+        <f>B3+C3+D3+E3-H3-I3-J3</f>
+      </c>
+      <c r="R3">
+        <f>R2+Q3</f>
+      </c>
+      <c r="S3">
+        <f>Q3-M3-N3</f>
+      </c>
+      <c r="T3">
+        <f>T2+S3</f>
+      </c>
+      <c r="W3">
+        <f>V3*W2</f>
+      </c>
+      <c r="AB3">
+        <f>Q3+W3+X3-Y3</f>
+      </c>
+      <c r="AC3">
+        <f>AC2+AB3</f>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -338,6 +359,27 @@
           <t>2月</t>
         </is>
       </c>
+      <c r="Q4">
+        <f>B4+C4+D4+E4-H4-I4-J4</f>
+      </c>
+      <c r="R4">
+        <f>R3+Q4</f>
+      </c>
+      <c r="S4">
+        <f>Q4-M4-N4</f>
+      </c>
+      <c r="T4">
+        <f>T3+S4</f>
+      </c>
+      <c r="W4">
+        <f>V4*W2</f>
+      </c>
+      <c r="AB4">
+        <f>Q4+W4+X4-Y4</f>
+      </c>
+      <c r="AC4">
+        <f>AC3+AB4</f>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -345,6 +387,27 @@
           <t>3月</t>
         </is>
       </c>
+      <c r="Q5">
+        <f>B5+C5+D5+E5-H5-I5-J5</f>
+      </c>
+      <c r="R5">
+        <f>R4+Q5</f>
+      </c>
+      <c r="S5">
+        <f>Q5-M5-N5</f>
+      </c>
+      <c r="T5">
+        <f>T4+S5</f>
+      </c>
+      <c r="W5">
+        <f>V5*W2</f>
+      </c>
+      <c r="AB5">
+        <f>Q5+W5+X5-Y5</f>
+      </c>
+      <c r="AC5">
+        <f>AC4+AB5</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -352,6 +415,27 @@
           <t>4月</t>
         </is>
       </c>
+      <c r="Q6">
+        <f>B6+C6+D6+E6-H6-I6-J6</f>
+      </c>
+      <c r="R6">
+        <f>R5+Q6</f>
+      </c>
+      <c r="S6">
+        <f>Q6-M6-N6</f>
+      </c>
+      <c r="T6">
+        <f>T5+S6</f>
+      </c>
+      <c r="W6">
+        <f>V6*W2</f>
+      </c>
+      <c r="AB6">
+        <f>Q6+W6+X6-Y6</f>
+      </c>
+      <c r="AC6">
+        <f>AC5+AB6</f>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -359,6 +443,27 @@
           <t>5月</t>
         </is>
       </c>
+      <c r="Q7">
+        <f>B7+C7+D7+E7-H7-I7-J7</f>
+      </c>
+      <c r="R7">
+        <f>R6+Q7</f>
+      </c>
+      <c r="S7">
+        <f>Q7-M7-N7</f>
+      </c>
+      <c r="T7">
+        <f>T6+S7</f>
+      </c>
+      <c r="W7">
+        <f>V7*W2</f>
+      </c>
+      <c r="AB7">
+        <f>Q7+W7+X7-Y7</f>
+      </c>
+      <c r="AC7">
+        <f>AC6+AB7</f>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -366,6 +471,27 @@
           <t>6月</t>
         </is>
       </c>
+      <c r="Q8">
+        <f>B8+C8+D8+E8-H8-I8-J8</f>
+      </c>
+      <c r="R8">
+        <f>R7+Q8</f>
+      </c>
+      <c r="S8">
+        <f>Q8-M8-N8</f>
+      </c>
+      <c r="T8">
+        <f>T7+S8</f>
+      </c>
+      <c r="W8">
+        <f>V8*W2</f>
+      </c>
+      <c r="AB8">
+        <f>Q8+W8+X8-Y8</f>
+      </c>
+      <c r="AC8">
+        <f>AC7+AB8</f>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -373,6 +499,27 @@
           <t>7月</t>
         </is>
       </c>
+      <c r="Q9">
+        <f>B9+C9+D9+E9-H9-I9-J9</f>
+      </c>
+      <c r="R9">
+        <f>R8+Q9</f>
+      </c>
+      <c r="S9">
+        <f>Q9-M9-N9</f>
+      </c>
+      <c r="T9">
+        <f>T8+S9</f>
+      </c>
+      <c r="W9">
+        <f>V9*W2</f>
+      </c>
+      <c r="AB9">
+        <f>Q9+W9+X9-Y9</f>
+      </c>
+      <c r="AC9">
+        <f>AC8+AB9</f>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -380,6 +527,27 @@
           <t>8月</t>
         </is>
       </c>
+      <c r="Q10">
+        <f>B10+C10+D10+E10-H10-I10-J10</f>
+      </c>
+      <c r="R10">
+        <f>R9+Q10</f>
+      </c>
+      <c r="S10">
+        <f>Q10-M10-N10</f>
+      </c>
+      <c r="T10">
+        <f>T9+S10</f>
+      </c>
+      <c r="W10">
+        <f>V10*W2</f>
+      </c>
+      <c r="AB10">
+        <f>Q10+W10+X10-Y10</f>
+      </c>
+      <c r="AC10">
+        <f>AC9+AB10</f>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -387,6 +555,27 @@
           <t>9月</t>
         </is>
       </c>
+      <c r="Q11">
+        <f>B11+C11+D11+E11-H11-I11-J11</f>
+      </c>
+      <c r="R11">
+        <f>R10+Q11</f>
+      </c>
+      <c r="S11">
+        <f>Q11-M11-N11</f>
+      </c>
+      <c r="T11">
+        <f>T10+S11</f>
+      </c>
+      <c r="W11">
+        <f>V11*W2</f>
+      </c>
+      <c r="AB11">
+        <f>Q11+W11+X11-Y11</f>
+      </c>
+      <c r="AC11">
+        <f>AC10+AB11</f>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -394,6 +583,27 @@
           <t>10月</t>
         </is>
       </c>
+      <c r="Q12">
+        <f>B12+C12+D12+E12-H12-I12-J12</f>
+      </c>
+      <c r="R12">
+        <f>R11+Q12</f>
+      </c>
+      <c r="S12">
+        <f>Q12-M12-N12</f>
+      </c>
+      <c r="T12">
+        <f>T11+S12</f>
+      </c>
+      <c r="W12">
+        <f>V12*W2</f>
+      </c>
+      <c r="AB12">
+        <f>Q12+W12+X12-Y12</f>
+      </c>
+      <c r="AC12">
+        <f>AC11+AB12</f>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -401,12 +611,54 @@
           <t>11月</t>
         </is>
       </c>
+      <c r="Q13">
+        <f>B13+C13+D13+E13-H13-I13-J13</f>
+      </c>
+      <c r="R13">
+        <f>R12+Q13</f>
+      </c>
+      <c r="S13">
+        <f>Q13-M13-N13</f>
+      </c>
+      <c r="T13">
+        <f>T12+S13</f>
+      </c>
+      <c r="W13">
+        <f>V13*W2</f>
+      </c>
+      <c r="AB13">
+        <f>Q13+W13+X13-Y13</f>
+      </c>
+      <c r="AC13">
+        <f>AC12+AB13</f>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
+      </c>
+      <c r="Q14">
+        <f>B14+C14+D14+E14-H14-I14-J14</f>
+      </c>
+      <c r="R14">
+        <f>R13+Q14</f>
+      </c>
+      <c r="S14">
+        <f>Q14-M14-N14</f>
+      </c>
+      <c r="T14">
+        <f>T13+S14</f>
+      </c>
+      <c r="W14">
+        <f>V14*W2</f>
+      </c>
+      <c r="AB14">
+        <f>Q14+W14+X14-Y14</f>
+      </c>
+      <c r="AC14">
+        <f>AC13+AB14</f>
       </c>
     </row>
     <row r="15"/>

--- a/skills/family-finance/assets/family-finance-template.xlsx
+++ b/skills/family-finance/assets/family-finance-template.xlsx
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="Q16">
-        <f>B16-H16</f>
+        <f>SUM(Q3:Q14)</f>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="Q17">
-        <f>Q16-M17</f>
+        <f>SUM(S3:S14)</f>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="AB17">
-        <f>Q16+V17</f>
+        <f>SUM(AB3:AB14)</f>
       </c>
     </row>
     <row r="18">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="H2">
-        <f>SUM(H3:H10)</f>
+        <f>SUM(H3:H6)</f>
       </c>
       <c r="I2">
         <v>0.4</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="H3">
-        <f>DIVIDE(G3,G18)</f>
+        <f>IFERROR(DIVIDE(G3,G13),0)</f>
       </c>
       <c r="I3">
         <v>0.05</v>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="H4">
-        <f>DIVIDE(G4,G18)</f>
+        <f>IFERROR(DIVIDE(G4,G13),0)</f>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="H5">
-        <f>DIVIDE(G5,G18)</f>
+        <f>IFERROR(DIVIDE(G5,G13),0)</f>
       </c>
       <c r="I5">
         <v>0.15</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="H6">
-        <f>DIVIDE(G6,G18)</f>
+        <f>IFERROR(DIVIDE(G6,G13),0)</f>
       </c>
       <c r="I6">
         <v>0.2</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="H7">
-        <f>SUM(H12:H14)</f>
+        <f>SUM(H8:H9)</f>
       </c>
       <c r="I7">
         <v>0.4</v>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="H8">
-        <f>DIVIDE(G12,G18)</f>
+        <f>IFERROR(DIVIDE(G8,G13),0)</f>
       </c>
       <c r="I8">
         <v>0.28</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="H9">
-        <f>DIVIDE(G13,G18)</f>
+        <f>IFERROR(DIVIDE(G9,G13),0)</f>
       </c>
     </row>
     <row r="10">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="H10">
-        <f>SUM(H16:H17)</f>
+        <f>SUM(H11:H12)</f>
       </c>
       <c r="I10">
         <v>0.2</v>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="H11">
-        <f>DIVIDE(G16,G18)</f>
+        <f>IFERROR(DIVIDE(G11,G13),0)</f>
       </c>
       <c r="I11">
         <v>0.2</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H12">
-        <f>DIVIDE(G17,G18)</f>
+        <f>IFERROR(DIVIDE(G12,G13),0)</f>
       </c>
     </row>
     <row r="13">
@@ -1079,8 +1079,8 @@
           <t>负债总计</t>
         </is>
       </c>
-      <c r="B13">
-        <f>SUM(C2:C17)</f>
+      <c r="C13">
+        <f>SUM(C2:C12)</f>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="F13">
-        <f>SUM(F3:F17)</f>
+        <f>SUM(F3:F12)</f>
       </c>
       <c r="G13">
-        <f>SUM(G3:G17)</f>
+        <f>SUM(G3:G12)</f>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="L13">
-        <f>SUM(L2:L17)</f>
+        <f>SUM(L2:L12)</f>
       </c>
       <c r="M13">
-        <f>SUM(M2:M17)</f>
+        <f>SUM(M2:M12)</f>
       </c>
     </row>
     <row r="14">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="L14">
-        <f>-B18+G18+M18</f>
+        <f>-C13+G13+M13</f>
       </c>
     </row>
   </sheetData>

--- a/skills/family-finance/assets/family-finance-template.xlsx
+++ b/skills/family-finance/assets/family-finance-template.xlsx
@@ -15,12 +15,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="13"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -33,7 +33,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F3FF"/>
+        <fgColor rgb="FFE1EAFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -50,9 +50,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -63,7 +67,7 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>家庭财务配置表</t>
         </is>
@@ -89,7 +93,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>2.0.0</t>
         </is>
       </c>
     </row>
@@ -101,7 +105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>2.0.0</t>
         </is>
       </c>
     </row>
@@ -115,27 +119,27 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>snapshot_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
+      <c r="B1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="C1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net_worth_wan</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -151,37 +155,37 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>operation_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
+      <c r="B1" t="inlineStr">
         <is>
           <t>preview_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="C1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr">
         <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ranges</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recovery_note</t>
         </is>
@@ -193,123 +197,182 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC18"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:AI18"/>
+  <sheetFormatPr defaultRowHeight="20.25"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="4.86" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="6" width="7.86" customWidth="1"/>
+    <col min="7" max="7" width="20.57" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="11" width="7.86" customWidth="1"/>
+    <col min="12" max="12" width="19.14" customWidth="1"/>
+    <col min="13" max="13" width="11.71" customWidth="1"/>
+    <col min="14" max="15" width="8.29" customWidth="1"/>
+    <col min="16" max="17" width="8" customWidth="1"/>
+    <col min="18" max="18" width="13.57" customWidth="1"/>
+    <col min="19" max="21" width="8" customWidth="1"/>
+    <col min="22" max="23" width="11.71" customWidth="1"/>
+    <col min="24" max="24" width="4.86" customWidth="1"/>
+    <col min="25" max="25" width="11.71" customWidth="1"/>
+    <col min="26" max="27" width="7.86" customWidth="1"/>
+    <col min="28" max="29" width="18.14" customWidth="1"/>
+    <col min="30" max="31" width="8" customWidth="1"/>
+    <col min="32" max="32" width="15.29" customWidth="1"/>
+    <col min="33" max="33" width="11.71" customWidth="1"/>
+    <col min="34" max="35" width="9.86" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1"/>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t>资
+产
+收
+支
+表</t>
+        </is>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
           <t>成员A工资</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t>成员B工资</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>公积金</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t>其他收入</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t>收入说明</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="H1" s="1"/>
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t>固定支出</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t>弹性支出</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t>特殊支出</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t>支出说明</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr" s="1">
+      <c r="M1" s="1"/>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t>公司股权/RSU数量</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t>公司股权/RSU金额</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t>资产收入</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t>资产减损</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t>资产收支说明</t>
+        </is>
+      </c>
+      <c r="S1" s="1"/>
+      <c r="T1" t="inlineStr" s="1">
+        <is>
+          <t>本行收支</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr" s="1">
+        <is>
+          <t>累计收支</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr" s="1">
+        <is>
+          <t>本行资产增量</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr" s="1">
+        <is>
+          <t>累计资产增量</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr" s="1">
+        <is>
+          <t>现
+金
+流
+表</t>
+        </is>
+      </c>
+      <c r="Y1" s="1"/>
+      <c r="Z1" t="inlineStr" s="1">
         <is>
           <t>定期转化</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr" s="1">
+      <c r="AA1" t="inlineStr" s="1">
         <is>
           <t>其他转化</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr" s="1">
+      <c r="AB1" t="inlineStr" s="1">
         <is>
           <t>资产转化说明</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr" s="1">
-        <is>
-          <t>本行收支</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr" s="1">
-        <is>
-          <t>累计收支</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr" s="1">
+      <c r="AC1" s="1"/>
+      <c r="AD1" t="inlineStr" s="1">
+        <is>
+          <t>定期赎回</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr" s="1">
+        <is>
+          <t>资产赎回</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr" s="1">
+        <is>
+          <t>资产赎回说明</t>
+        </is>
+      </c>
+      <c r="AG1" s="1"/>
+      <c r="AH1" t="inlineStr" s="1">
         <is>
           <t>本行现金流</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr" s="1">
-        <is>
-          <t>剩余现金</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr" s="1">
-        <is>
-          <t>公司股权/RSU数量</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr" s="1">
-        <is>
-          <t>公司股权/RSU金额</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr" s="1">
-        <is>
-          <t>资产收入</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr" s="1">
-        <is>
-          <t>资产减损</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr" s="1">
-        <is>
-          <t>资产收支说明</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr" s="1">
-        <is>
-          <t>本行资产变化</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr" s="1">
-        <is>
-          <t>累计资产变化</t>
+      <c r="AI1" t="inlineStr" s="1">
+        <is>
+          <t>累计现金流</t>
         </is>
       </c>
     </row>
@@ -319,11 +382,13 @@
           <t>起始</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="B2" s="1"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>RSU计价</t>
         </is>
       </c>
+      <c r="X2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -331,26 +396,28 @@
           <t>1月</t>
         </is>
       </c>
-      <c r="Q3">
-        <f>B3+C3+D3+E3-H3-I3-J3</f>
-      </c>
-      <c r="R3">
-        <f>R2+Q3</f>
-      </c>
-      <c r="S3">
-        <f>Q3-M3-N3</f>
+      <c r="B3" s="1"/>
+      <c r="O3">
+        <f>N3*O2</f>
       </c>
       <c r="T3">
-        <f>T2+S3</f>
+        <f>D3+E3+F3-I3-J3-K3</f>
+      </c>
+      <c r="U3">
+        <f>U2+T3</f>
+      </c>
+      <c r="V3">
+        <f>T3+O3+P3-Q3</f>
       </c>
       <c r="W3">
-        <f>V3*W2</f>
-      </c>
-      <c r="AB3">
-        <f>Q3+W3+X3-Y3</f>
-      </c>
-      <c r="AC3">
-        <f>AC2+AB3</f>
+        <f>W2+V3</f>
+      </c>
+      <c r="X3" s="1"/>
+      <c r="AH3">
+        <f>T3-Z3-AA3+AD3+AE3</f>
+      </c>
+      <c r="AI3">
+        <f>AI2+AH3</f>
       </c>
     </row>
     <row r="4">
@@ -359,26 +426,28 @@
           <t>2月</t>
         </is>
       </c>
-      <c r="Q4">
-        <f>B4+C4+D4+E4-H4-I4-J4</f>
-      </c>
-      <c r="R4">
-        <f>R3+Q4</f>
-      </c>
-      <c r="S4">
-        <f>Q4-M4-N4</f>
+      <c r="B4" s="1"/>
+      <c r="O4">
+        <f>N4*O2</f>
       </c>
       <c r="T4">
-        <f>T3+S4</f>
+        <f>D4+E4+F4-I4-J4-K4</f>
+      </c>
+      <c r="U4">
+        <f>U3+T4</f>
+      </c>
+      <c r="V4">
+        <f>T4+O4+P4-Q4</f>
       </c>
       <c r="W4">
-        <f>V4*W2</f>
-      </c>
-      <c r="AB4">
-        <f>Q4+W4+X4-Y4</f>
-      </c>
-      <c r="AC4">
-        <f>AC3+AB4</f>
+        <f>W3+V4</f>
+      </c>
+      <c r="X4" s="1"/>
+      <c r="AH4">
+        <f>T4-Z4-AA4+AD4+AE4</f>
+      </c>
+      <c r="AI4">
+        <f>AI3+AH4</f>
       </c>
     </row>
     <row r="5">
@@ -387,26 +456,28 @@
           <t>3月</t>
         </is>
       </c>
-      <c r="Q5">
-        <f>B5+C5+D5+E5-H5-I5-J5</f>
-      </c>
-      <c r="R5">
-        <f>R4+Q5</f>
-      </c>
-      <c r="S5">
-        <f>Q5-M5-N5</f>
+      <c r="B5" s="1"/>
+      <c r="O5">
+        <f>N5*O2</f>
       </c>
       <c r="T5">
-        <f>T4+S5</f>
+        <f>D5+E5+F5-I5-J5-K5</f>
+      </c>
+      <c r="U5">
+        <f>U4+T5</f>
+      </c>
+      <c r="V5">
+        <f>T5+O5+P5-Q5</f>
       </c>
       <c r="W5">
-        <f>V5*W2</f>
-      </c>
-      <c r="AB5">
-        <f>Q5+W5+X5-Y5</f>
-      </c>
-      <c r="AC5">
-        <f>AC4+AB5</f>
+        <f>W4+V5</f>
+      </c>
+      <c r="X5" s="1"/>
+      <c r="AH5">
+        <f>T5-Z5-AA5+AD5+AE5</f>
+      </c>
+      <c r="AI5">
+        <f>AI4+AH5</f>
       </c>
     </row>
     <row r="6">
@@ -415,26 +486,28 @@
           <t>4月</t>
         </is>
       </c>
-      <c r="Q6">
-        <f>B6+C6+D6+E6-H6-I6-J6</f>
-      </c>
-      <c r="R6">
-        <f>R5+Q6</f>
-      </c>
-      <c r="S6">
-        <f>Q6-M6-N6</f>
+      <c r="B6" s="1"/>
+      <c r="O6">
+        <f>N6*O2</f>
       </c>
       <c r="T6">
-        <f>T5+S6</f>
+        <f>D6+E6+F6-I6-J6-K6</f>
+      </c>
+      <c r="U6">
+        <f>U5+T6</f>
+      </c>
+      <c r="V6">
+        <f>T6+O6+P6-Q6</f>
       </c>
       <c r="W6">
-        <f>V6*W2</f>
-      </c>
-      <c r="AB6">
-        <f>Q6+W6+X6-Y6</f>
-      </c>
-      <c r="AC6">
-        <f>AC5+AB6</f>
+        <f>W5+V6</f>
+      </c>
+      <c r="X6" s="1"/>
+      <c r="AH6">
+        <f>T6-Z6-AA6+AD6+AE6</f>
+      </c>
+      <c r="AI6">
+        <f>AI5+AH6</f>
       </c>
     </row>
     <row r="7">
@@ -443,26 +516,28 @@
           <t>5月</t>
         </is>
       </c>
-      <c r="Q7">
-        <f>B7+C7+D7+E7-H7-I7-J7</f>
-      </c>
-      <c r="R7">
-        <f>R6+Q7</f>
-      </c>
-      <c r="S7">
-        <f>Q7-M7-N7</f>
+      <c r="B7" s="1"/>
+      <c r="O7">
+        <f>N7*O2</f>
       </c>
       <c r="T7">
-        <f>T6+S7</f>
+        <f>D7+E7+F7-I7-J7-K7</f>
+      </c>
+      <c r="U7">
+        <f>U6+T7</f>
+      </c>
+      <c r="V7">
+        <f>T7+O7+P7-Q7</f>
       </c>
       <c r="W7">
-        <f>V7*W2</f>
-      </c>
-      <c r="AB7">
-        <f>Q7+W7+X7-Y7</f>
-      </c>
-      <c r="AC7">
-        <f>AC6+AB7</f>
+        <f>W6+V7</f>
+      </c>
+      <c r="X7" s="1"/>
+      <c r="AH7">
+        <f>T7-Z7-AA7+AD7+AE7</f>
+      </c>
+      <c r="AI7">
+        <f>AI6+AH7</f>
       </c>
     </row>
     <row r="8">
@@ -471,26 +546,28 @@
           <t>6月</t>
         </is>
       </c>
-      <c r="Q8">
-        <f>B8+C8+D8+E8-H8-I8-J8</f>
-      </c>
-      <c r="R8">
-        <f>R7+Q8</f>
-      </c>
-      <c r="S8">
-        <f>Q8-M8-N8</f>
+      <c r="B8" s="1"/>
+      <c r="O8">
+        <f>N8*O2</f>
       </c>
       <c r="T8">
-        <f>T7+S8</f>
+        <f>D8+E8+F8-I8-J8-K8</f>
+      </c>
+      <c r="U8">
+        <f>U7+T8</f>
+      </c>
+      <c r="V8">
+        <f>T8+O8+P8-Q8</f>
       </c>
       <c r="W8">
-        <f>V8*W2</f>
-      </c>
-      <c r="AB8">
-        <f>Q8+W8+X8-Y8</f>
-      </c>
-      <c r="AC8">
-        <f>AC7+AB8</f>
+        <f>W7+V8</f>
+      </c>
+      <c r="X8" s="1"/>
+      <c r="AH8">
+        <f>T8-Z8-AA8+AD8+AE8</f>
+      </c>
+      <c r="AI8">
+        <f>AI7+AH8</f>
       </c>
     </row>
     <row r="9">
@@ -499,26 +576,28 @@
           <t>7月</t>
         </is>
       </c>
-      <c r="Q9">
-        <f>B9+C9+D9+E9-H9-I9-J9</f>
-      </c>
-      <c r="R9">
-        <f>R8+Q9</f>
-      </c>
-      <c r="S9">
-        <f>Q9-M9-N9</f>
+      <c r="B9" s="1"/>
+      <c r="O9">
+        <f>N9*O2</f>
       </c>
       <c r="T9">
-        <f>T8+S9</f>
+        <f>D9+E9+F9-I9-J9-K9</f>
+      </c>
+      <c r="U9">
+        <f>U8+T9</f>
+      </c>
+      <c r="V9">
+        <f>T9+O9+P9-Q9</f>
       </c>
       <c r="W9">
-        <f>V9*W2</f>
-      </c>
-      <c r="AB9">
-        <f>Q9+W9+X9-Y9</f>
-      </c>
-      <c r="AC9">
-        <f>AC8+AB9</f>
+        <f>W8+V9</f>
+      </c>
+      <c r="X9" s="1"/>
+      <c r="AH9">
+        <f>T9-Z9-AA9+AD9+AE9</f>
+      </c>
+      <c r="AI9">
+        <f>AI8+AH9</f>
       </c>
     </row>
     <row r="10">
@@ -527,26 +606,28 @@
           <t>8月</t>
         </is>
       </c>
-      <c r="Q10">
-        <f>B10+C10+D10+E10-H10-I10-J10</f>
-      </c>
-      <c r="R10">
-        <f>R9+Q10</f>
-      </c>
-      <c r="S10">
-        <f>Q10-M10-N10</f>
+      <c r="B10" s="1"/>
+      <c r="O10">
+        <f>N10*O2</f>
       </c>
       <c r="T10">
-        <f>T9+S10</f>
+        <f>D10+E10+F10-I10-J10-K10</f>
+      </c>
+      <c r="U10">
+        <f>U9+T10</f>
+      </c>
+      <c r="V10">
+        <f>T10+O10+P10-Q10</f>
       </c>
       <c r="W10">
-        <f>V10*W2</f>
-      </c>
-      <c r="AB10">
-        <f>Q10+W10+X10-Y10</f>
-      </c>
-      <c r="AC10">
-        <f>AC9+AB10</f>
+        <f>W9+V10</f>
+      </c>
+      <c r="X10" s="1"/>
+      <c r="AH10">
+        <f>T10-Z10-AA10+AD10+AE10</f>
+      </c>
+      <c r="AI10">
+        <f>AI9+AH10</f>
       </c>
     </row>
     <row r="11">
@@ -555,26 +636,28 @@
           <t>9月</t>
         </is>
       </c>
-      <c r="Q11">
-        <f>B11+C11+D11+E11-H11-I11-J11</f>
-      </c>
-      <c r="R11">
-        <f>R10+Q11</f>
-      </c>
-      <c r="S11">
-        <f>Q11-M11-N11</f>
+      <c r="B11" s="1"/>
+      <c r="O11">
+        <f>N11*O2</f>
       </c>
       <c r="T11">
-        <f>T10+S11</f>
+        <f>D11+E11+F11-I11-J11-K11</f>
+      </c>
+      <c r="U11">
+        <f>U10+T11</f>
+      </c>
+      <c r="V11">
+        <f>T11+O11+P11-Q11</f>
       </c>
       <c r="W11">
-        <f>V11*W2</f>
-      </c>
-      <c r="AB11">
-        <f>Q11+W11+X11-Y11</f>
-      </c>
-      <c r="AC11">
-        <f>AC10+AB11</f>
+        <f>W10+V11</f>
+      </c>
+      <c r="X11" s="1"/>
+      <c r="AH11">
+        <f>T11-Z11-AA11+AD11+AE11</f>
+      </c>
+      <c r="AI11">
+        <f>AI10+AH11</f>
       </c>
     </row>
     <row r="12">
@@ -583,26 +666,28 @@
           <t>10月</t>
         </is>
       </c>
-      <c r="Q12">
-        <f>B12+C12+D12+E12-H12-I12-J12</f>
-      </c>
-      <c r="R12">
-        <f>R11+Q12</f>
-      </c>
-      <c r="S12">
-        <f>Q12-M12-N12</f>
+      <c r="B12" s="1"/>
+      <c r="O12">
+        <f>N12*O2</f>
       </c>
       <c r="T12">
-        <f>T11+S12</f>
+        <f>D12+E12+F12-I12-J12-K12</f>
+      </c>
+      <c r="U12">
+        <f>U11+T12</f>
+      </c>
+      <c r="V12">
+        <f>T12+O12+P12-Q12</f>
       </c>
       <c r="W12">
-        <f>V12*W2</f>
-      </c>
-      <c r="AB12">
-        <f>Q12+W12+X12-Y12</f>
-      </c>
-      <c r="AC12">
-        <f>AC11+AB12</f>
+        <f>W11+V12</f>
+      </c>
+      <c r="X12" s="1"/>
+      <c r="AH12">
+        <f>T12-Z12-AA12+AD12+AE12</f>
+      </c>
+      <c r="AI12">
+        <f>AI11+AH12</f>
       </c>
     </row>
     <row r="13">
@@ -611,26 +696,28 @@
           <t>11月</t>
         </is>
       </c>
-      <c r="Q13">
-        <f>B13+C13+D13+E13-H13-I13-J13</f>
-      </c>
-      <c r="R13">
-        <f>R12+Q13</f>
-      </c>
-      <c r="S13">
-        <f>Q13-M13-N13</f>
+      <c r="B13" s="1"/>
+      <c r="O13">
+        <f>N13*O2</f>
       </c>
       <c r="T13">
-        <f>T12+S13</f>
+        <f>D13+E13+F13-I13-J13-K13</f>
+      </c>
+      <c r="U13">
+        <f>U12+T13</f>
+      </c>
+      <c r="V13">
+        <f>T13+O13+P13-Q13</f>
       </c>
       <c r="W13">
-        <f>V13*W2</f>
-      </c>
-      <c r="AB13">
-        <f>Q13+W13+X13-Y13</f>
-      </c>
-      <c r="AC13">
-        <f>AC12+AB13</f>
+        <f>W12+V13</f>
+      </c>
+      <c r="X13" s="1"/>
+      <c r="AH13">
+        <f>T13-Z13-AA13+AD13+AE13</f>
+      </c>
+      <c r="AI13">
+        <f>AI12+AH13</f>
       </c>
     </row>
     <row r="14">
@@ -639,40 +726,40 @@
           <t>12月</t>
         </is>
       </c>
-      <c r="Q14">
-        <f>B14+C14+D14+E14-H14-I14-J14</f>
-      </c>
-      <c r="R14">
-        <f>R13+Q14</f>
-      </c>
-      <c r="S14">
-        <f>Q14-M14-N14</f>
+      <c r="B14" s="1"/>
+      <c r="O14">
+        <f>N14*O2</f>
       </c>
       <c r="T14">
-        <f>T13+S14</f>
+        <f>D14+E14+F14-I14-J14-K14</f>
+      </c>
+      <c r="U14">
+        <f>U13+T14</f>
+      </c>
+      <c r="V14">
+        <f>T14+O14+P14-Q14</f>
       </c>
       <c r="W14">
-        <f>V14*W2</f>
-      </c>
-      <c r="AB14">
-        <f>Q14+W14+X14-Y14</f>
-      </c>
-      <c r="AC14">
-        <f>AC13+AB14</f>
-      </c>
-    </row>
-    <row r="15"/>
+        <f>W13+V14</f>
+      </c>
+      <c r="X14" s="1"/>
+      <c r="AH14">
+        <f>T14-Z14-AA14+AD14+AE14</f>
+      </c>
+      <c r="AI14">
+        <f>AI13+AH14</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1"/>
+      <c r="X15" s="1"/>
+    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B16" s="1"/>
+      <c r="C16" t="inlineStr" s="1">
         <is>
           <t>收入小记</t>
         </is>
-      </c>
-      <c r="B16">
-        <f>SUM(B3:B14)</f>
-      </c>
-      <c r="C16">
-        <f>SUM(C3:C14)</f>
       </c>
       <c r="D16">
         <f>SUM(D3:D14)</f>
@@ -680,13 +767,13 @@
       <c r="E16">
         <f>SUM(E3:E14)</f>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16">
+        <f>SUM(F3:F14)</f>
+      </c>
+      <c r="H16" t="inlineStr" s="1">
         <is>
           <t>支出小记</t>
         </is>
-      </c>
-      <c r="H16">
-        <f>SUM(H3:H14)</f>
       </c>
       <c r="I16">
         <f>SUM(I3:I14)</f>
@@ -694,153 +781,221 @@
       <c r="J16">
         <f>SUM(J3:J14)</f>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>资产转化小计</t>
-        </is>
-      </c>
-      <c r="M16">
-        <f>SUM(M3:M14)</f>
+      <c r="K16">
+        <f>SUM(K3:K14)</f>
+      </c>
+      <c r="M16" t="inlineStr" s="1">
+        <is>
+          <t>资产小记</t>
+        </is>
       </c>
       <c r="N16">
         <f>SUM(N3:N14)</f>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>收支结余</t>
-        </is>
+      <c r="O16">
+        <f>SUM(O3:O14)</f>
+      </c>
+      <c r="P16">
+        <f>SUM(P3:P14)</f>
       </c>
       <c r="Q16">
         <f>SUM(Q3:Q14)</f>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>资产小记</t>
-        </is>
-      </c>
-      <c r="V16">
-        <f>SUM(V3:V14)</f>
-      </c>
-      <c r="W16">
-        <f>SUM(W3:W14)</f>
-      </c>
-      <c r="X16">
-        <f>SUM(X3:X14)</f>
-      </c>
-      <c r="Y16">
-        <f>SUM(Y3:Y14)</f>
+      <c r="S16" t="inlineStr" s="1">
+        <is>
+          <t>现金结余</t>
+        </is>
+      </c>
+      <c r="T16">
+        <f>D17-I17</f>
+      </c>
+      <c r="X16" s="1"/>
+      <c r="Y16" t="inlineStr" s="1">
+        <is>
+          <t>资产转化小计</t>
+        </is>
+      </c>
+      <c r="Z16">
+        <f>SUM(Z3:Z14)</f>
+      </c>
+      <c r="AA16">
+        <f>SUM(AA3:AA14)</f>
+      </c>
+      <c r="AC16" t="inlineStr" s="1">
+        <is>
+          <t>资产赎回小计</t>
+        </is>
+      </c>
+      <c r="AD16">
+        <f>SUM(AD3:AD14)</f>
+      </c>
+      <c r="AE16">
+        <f>SUM(AE3:AE14)</f>
+      </c>
+      <c r="AG16" t="inlineStr" s="1">
+        <is>
+          <t>现金净增加额</t>
+        </is>
+      </c>
+      <c r="AH16">
+        <f>T16-Z17+AD17</f>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B17" s="1"/>
+      <c r="C17" t="inlineStr" s="1">
         <is>
           <t>收入总计</t>
         </is>
       </c>
-      <c r="B17">
-        <f>SUM(B16:E16)</f>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="D17">
+        <f>SUM(D16:F16)</f>
+      </c>
+      <c r="H17" t="inlineStr" s="1">
         <is>
           <t>支出总计</t>
         </is>
       </c>
-      <c r="H17">
-        <f>SUM(H16:J16)</f>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="I17">
+        <f>SUM(I16:K16)</f>
+      </c>
+      <c r="M17" t="inlineStr" s="1">
+        <is>
+          <t>资产收支总计</t>
+        </is>
+      </c>
+      <c r="N17">
+        <f>O16+P16-Q16</f>
+      </c>
+      <c r="S17" t="inlineStr" s="1">
+        <is>
+          <t>资产结余</t>
+        </is>
+      </c>
+      <c r="T17">
+        <f>T16+N17</f>
+      </c>
+      <c r="X17" s="1"/>
+      <c r="Y17" t="inlineStr" s="1">
         <is>
           <t>资产转化总计</t>
         </is>
       </c>
-      <c r="M17">
-        <f>M16+N16</f>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>现金结余</t>
-        </is>
-      </c>
-      <c r="Q17">
-        <f>SUM(S3:S14)</f>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>资产收支总计</t>
-        </is>
-      </c>
-      <c r="V17">
-        <f>W16+X16-Y16</f>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>资产变化总计</t>
-        </is>
-      </c>
-      <c r="AB17">
-        <f>SUM(AB3:AB14)</f>
-      </c>
+      <c r="Z17">
+        <f>Z16+AA16</f>
+      </c>
+      <c r="AC17" t="inlineStr" s="1">
+        <is>
+          <t>资产赎回总计</t>
+        </is>
+      </c>
+      <c r="AD17">
+        <f>AD16+AE16</f>
+      </c>
+      <c r="AG17" s="1"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B18" s="1"/>
+      <c r="C18" t="inlineStr" s="1">
         <is>
           <t>收入说明</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>记录工资、公积金、奖金、退税等收入。非周期收入写入其他收入并补充说明。</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>主要记录工资等现金收入；奖金、退税等非周期收入记入“其他收入”并补充说明。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr" s="1">
         <is>
           <t>支出说明</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>固定支出记录房贷、租金、保险等稳定支出；弹性支出记录生活消费；特殊支出记录非周期大额事项。</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>固定支出记录房贷利息、租金、保险等稳定支出；弹性支出记录生活消费；特殊支出记录非周期大额事项。</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr" s="1">
+        <is>
+          <t>资产收支说明</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>资产收入记录没有经过现金账户、直接增加资产的项目，例如住房公积金；公司股权/RSU单独列出。资产减损记录折旧或其他资产损失。</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr" s="1">
+        <is>
+          <t>结余说明</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>现金结余为收入减支出；资产结余为现金结余加非现金资产净增加。</t>
+        </is>
+      </c>
+      <c r="X18" s="1"/>
+      <c r="Y18" t="inlineStr" s="1">
         <is>
           <t>资产转化说明</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>记录现金转为资产、还贷款本金、长期账户入金等不改变净资产但影响现金流的事项。</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>结余说明</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>建议保留覆盖 6-12 个月必要支出的现金安全垫。</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>资产收支说明</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>记录公司股权、资产收入、资产减损、固定资产折旧等不一定经过现金账户的资产变化。</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>记录现金转为其他资产或偿还债务本金的事项；这些事项影响现金流，但不直接改变净资产。</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr" s="1">
+        <is>
+          <t>资产赎回说明</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>记录资产赎回或出售后转为现金的事项；这些事项影响现金流，但不直接改变净资产。</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr" s="1">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>为保护隐私，本表只展示现金净增加额，不记录期初或期末现金余额。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B1:B18"/>
+    <mergeCell ref="X1:X18"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="N18:R18"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="Z17:AA17"/>
+    <mergeCell ref="Z18:AB18"/>
+    <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="AD18:AF18"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="AH16:AI17"/>
+    <mergeCell ref="AH18:AI18"/>
+  </mergeCells>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="20.25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
@@ -858,6 +1013,7 @@
           <t>现值(万)</t>
         </is>
       </c>
+      <c r="D1" s="1"/>
       <c r="E1" t="inlineStr" s="1">
         <is>
           <t>流动资产项</t>
@@ -883,6 +1039,7 @@
           <t>未来合理占比</t>
         </is>
       </c>
+      <c r="J1" s="1"/>
       <c r="K1" t="inlineStr" s="1">
         <is>
           <t>非流动资产项</t>
@@ -905,15 +1062,18 @@
           <t>住房贷款</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="B2" s="2"/>
+      <c r="E2" t="inlineStr" s="1">
         <is>
           <t>防御层</t>
         </is>
       </c>
-      <c r="H2">
-        <f>SUM(H3:H6)</f>
-      </c>
-      <c r="I2">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="3">
+        <f>SUM(H3:H10)</f>
+      </c>
+      <c r="I2" s="4">
         <v>0.4</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,16 +1088,20 @@
           <t>消费贷/备用贷款</t>
         </is>
       </c>
+      <c r="B3" s="2"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>现金及短债</t>
-        </is>
-      </c>
-      <c r="H3">
-        <f>IFERROR(DIVIDE(G3,G13),0)</f>
-      </c>
-      <c r="I3">
-        <v>0.05</v>
+          <t>现金</t>
+        </is>
+      </c>
+      <c r="H3" s="2">
+        <f>IFERROR(G3/G20,0)</f>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>现金与公积金
+5%</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -951,13 +1115,14 @@
           <t>车贷</t>
         </is>
       </c>
+      <c r="B4" s="2"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>公积金账户</t>
         </is>
       </c>
-      <c r="H4">
-        <f>IFERROR(DIVIDE(G4,G13),0)</f>
+      <c r="H4" s="2">
+        <f>IFERROR(G4/G20,0)</f>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -966,155 +1131,262 @@
       </c>
     </row>
     <row r="5">
+      <c r="B5" s="2"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>中短期债券</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f>IFERROR(G5/G20,0)</f>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>债券与定存
+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>定期存款</t>
+        </is>
+      </c>
+      <c r="H6" s="2">
+        <f>IFERROR(G6/G20,0)</f>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>外币定存</t>
+        </is>
+      </c>
+      <c r="H7" s="2">
+        <f>IFERROR(G7/G20,0)</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>短期美债</t>
+        </is>
+      </c>
+      <c r="H8" s="2">
+        <f>IFERROR(G8/G20,0)</f>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2"/>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>实物黄金</t>
         </is>
       </c>
-      <c r="H5">
-        <f>IFERROR(DIVIDE(G5,G13),0)</f>
-      </c>
-      <c r="I5">
-        <v>0.15</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="H9" s="2">
+        <f>IFERROR(G9/G20,0)</f>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>黄金
+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>黄金积存</t>
+        </is>
+      </c>
+      <c r="H10" s="2">
+        <f>IFERROR(G10/G20,0)</f>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2"/>
+      <c r="E11" t="inlineStr" s="1">
+        <is>
+          <t>Beta层</t>
+        </is>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="3">
+        <f>SUM(H12:H15)</f>
+      </c>
+      <c r="I11" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>境内宽基基金</t>
+        </is>
+      </c>
+      <c r="H12" s="2">
+        <f>IFERROR(G12/G20,0)</f>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>宽基指数
+35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>海外指数账户</t>
+        </is>
+      </c>
+      <c r="H13" s="2">
+        <f>IFERROR(G13/G20,0)</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>个人养老金账户A</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>贷款备还金</t>
-        </is>
-      </c>
-      <c r="H6">
-        <f>IFERROR(DIVIDE(G6,G13),0)</f>
-      </c>
-      <c r="I6">
+      <c r="H14" s="2">
+        <f>IFERROR(G14/G20,0)</f>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>个人养老金
+5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>个人养老金账户B</t>
+        </is>
+      </c>
+      <c r="H15" s="2">
+        <f>IFERROR(G15/G20,0)</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+      <c r="E16" t="inlineStr" s="1">
+        <is>
+          <t>Alpha层</t>
+        </is>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="3">
+        <f>SUM(H17:H19)</f>
+      </c>
+      <c r="I16" s="4">
         <v>0.2</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>个人养老金账户B</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Beta层</t>
-        </is>
-      </c>
-      <c r="H7">
-        <f>SUM(H8:H9)</f>
-      </c>
-      <c r="I7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>宽基基金账户</t>
-        </is>
-      </c>
-      <c r="H8">
-        <f>IFERROR(DIVIDE(G8,G13),0)</f>
-      </c>
-      <c r="I8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>海外指数账户</t>
-        </is>
-      </c>
-      <c r="H9">
-        <f>IFERROR(DIVIDE(G9,G13),0)</f>
-      </c>
-    </row>
-    <row r="10">
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Alpha层</t>
-        </is>
-      </c>
-      <c r="H10">
-        <f>SUM(H11:H12)</f>
-      </c>
-      <c r="I10">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="E11" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="B17" s="2"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>个股/主动账户</t>
         </is>
       </c>
-      <c r="H11">
-        <f>IFERROR(DIVIDE(G11,G13),0)</f>
-      </c>
-      <c r="I11">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="E12" t="inlineStr">
+      <c r="H17" s="2">
+        <f>IFERROR(G17/G20,0)</f>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>主动投资
+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>数字资产</t>
+        </is>
+      </c>
+      <c r="H18" s="2">
+        <f>IFERROR(G18/G20,0)</f>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>公司股权/RSU</t>
         </is>
       </c>
-      <c r="H12">
-        <f>IFERROR(DIVIDE(G12,G13),0)</f>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="H19" s="2">
+        <f>IFERROR(G19/G20,0)</f>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="1">
         <is>
           <t>负债总计</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C2:C12)</f>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="B20">
+        <f>SUM(C2:C19)</f>
+      </c>
+      <c r="E20" t="inlineStr" s="1">
         <is>
           <t>流动资产总计</t>
         </is>
       </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-      </c>
-      <c r="G13">
-        <f>SUM(G3:G12)</f>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="F20">
+        <f>SUM(F3:F19)</f>
+      </c>
+      <c r="G20">
+        <f>SUM(G3:G19)</f>
+      </c>
+      <c r="K20" t="inlineStr" s="1">
         <is>
           <t>固定资产总计</t>
         </is>
       </c>
-      <c r="L13">
-        <f>SUM(L2:L12)</f>
-      </c>
-      <c r="M13">
-        <f>SUM(M2:M12)</f>
-      </c>
-    </row>
-    <row r="14">
-      <c r="K14" t="inlineStr">
+      <c r="L20">
+        <f>SUM(L2:L19)</f>
+      </c>
+      <c r="M20">
+        <f>SUM(M2:M19)</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="K21" t="inlineStr" s="1">
         <is>
           <t>净资产</t>
         </is>
       </c>
-      <c r="L14">
-        <f>-C13+G13+M13</f>
+      <c r="L21">
+        <f>-B20+G20+M20</f>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="L21:M21"/>
+  </mergeCells>
 </worksheet>
 </file>